--- a/resources/combat/combat.xlsx
+++ b/resources/combat/combat.xlsx
@@ -1780,7 +1780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:T39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.125" customWidth="1" style="3" min="1" max="1"/>
@@ -3733,6 +3733,56 @@
       <c r="N37" s="7" t="n"/>
       <c r="O37" s="14" t="n"/>
     </row>
+    <row r="38">
+      <c r="A38" s="14" t="n">
+        <v>100140006</v>
+      </c>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>BOSS</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n">
+        <v>10052</v>
+      </c>
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
+      <c r="I38" s="7" t="n"/>
+      <c r="J38" s="7" t="n"/>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
+      <c r="N38" s="7" t="n"/>
+      <c r="O38" s="14" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="n">
+        <v>100140007</v>
+      </c>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>BOSS</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n">
+        <v>10053</v>
+      </c>
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="22" t="n"/>
+      <c r="H39" s="22" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="7" t="n"/>
+      <c r="K39" s="7" t="n"/>
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
+      <c r="N39" s="7" t="n"/>
+      <c r="O39" s="14" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A14">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>

--- a/resources/combat/combat.xlsx
+++ b/resources/combat/combat.xlsx
@@ -1780,7 +1780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.125" customWidth="1" style="3" min="1" max="1"/>
@@ -2700,62 +2700,68 @@
       <c r="T18" s="9" t="n"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="15">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>25060001</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>清剿战斗</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>pve</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>10050</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>100600</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="9" t="n"/>
-      <c r="S19" s="9" t="n"/>
-      <c r="T19" s="9" t="n"/>
+      <c r="A19" s="7" t="n">
+        <v>100011000</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>低级灵脉战</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>10033</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="15">
       <c r="A20" s="7" t="n">
-        <v>100011000</v>
+        <v>100011001</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>低级灵脉战</t>
+          <t>中级灵脉战</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
@@ -2766,7 +2772,7 @@
         <v>10005</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>10033</v>
+        <v>10034</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>3000</v>
@@ -2774,8 +2780,8 @@
       <c r="J20" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="K20" s="9" t="n">
-        <v>0</v>
+      <c r="K20" s="7" t="n">
+        <v>3001</v>
       </c>
       <c r="L20" s="9" t="n">
         <v>0</v>
@@ -2807,11 +2813,11 @@
     </row>
     <row r="21" ht="16.5" customHeight="1" s="15">
       <c r="A21" s="7" t="n">
-        <v>100011001</v>
+        <v>100011002</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>中级灵脉战</t>
+          <t>高级灵脉战</t>
         </is>
       </c>
       <c r="C21" s="8" t="n"/>
@@ -2822,7 +2828,7 @@
         <v>10005</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>10034</v>
+        <v>10035</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>3000</v>
@@ -2833,8 +2839,8 @@
       <c r="K21" s="7" t="n">
         <v>3001</v>
       </c>
-      <c r="L21" s="9" t="n">
-        <v>0</v>
+      <c r="L21" s="7" t="n">
+        <v>3001</v>
       </c>
       <c r="M21" s="9" t="n">
         <v>0</v>
@@ -2862,15 +2868,19 @@
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="15">
-      <c r="A22" s="7" t="n">
-        <v>100011002</v>
+      <c r="A22" s="14" t="n">
+        <v>100080001</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>高级灵脉战</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n"/>
+          <t>洞府土地庙1-1</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>TEMPLE</t>
+        </is>
+      </c>
       <c r="D22" s="8" t="n">
         <v>1</v>
       </c>
@@ -2878,19 +2888,19 @@
         <v>10005</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>10035</v>
+        <v>10044</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>3001</v>
+        <v>3002</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>3001</v>
+        <v>3003</v>
       </c>
       <c r="M22" s="9" t="n">
         <v>0</v>
@@ -2919,11 +2929,11 @@
     </row>
     <row r="23" ht="16.5" customHeight="1" s="15">
       <c r="A23" s="14" t="n">
-        <v>100080001</v>
+        <v>100080002</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-1</t>
+          <t>洞府土地庙1-2</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2938,25 +2948,25 @@
         <v>10005</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>10044</v>
-      </c>
-      <c r="I23" s="7" t="n">
+        <v>10068</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="7" t="n">
         <v>3002</v>
       </c>
-      <c r="J23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="7" t="n">
-        <v>3003</v>
+      <c r="L23" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="9" t="n">
-        <v>0</v>
+      <c r="N23" s="7" t="n">
+        <v>3004</v>
       </c>
       <c r="O23" s="9" t="n">
         <v>0</v>
@@ -2979,11 +2989,11 @@
     </row>
     <row r="24" ht="16.5" customHeight="1" s="15">
       <c r="A24" s="14" t="n">
-        <v>100080002</v>
+        <v>100080003</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-2</t>
+          <t>洞府土地庙1-3</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -2998,7 +3008,7 @@
         <v>10005</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>10068</v>
+        <v>10050</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>0</v>
@@ -3006,17 +3016,17 @@
       <c r="J24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>3003</v>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="7" t="n">
         <v>3002</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>3004</v>
       </c>
       <c r="O24" s="9" t="n">
         <v>0</v>
@@ -3039,11 +3049,11 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" s="15">
       <c r="A25" s="14" t="n">
-        <v>100080003</v>
+        <v>100080004</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-3</t>
+          <t>洞府土地庙1-4</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3058,37 +3068,37 @@
         <v>10005</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>10050</v>
+        <v>10070</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="9" t="n">
-        <v>0</v>
+      <c r="J25" s="7" t="n">
+        <v>3003</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="L25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>3004</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="7" t="n">
         <v>3003</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="O25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="S25" s="9" t="n">
         <v>0</v>
@@ -3099,11 +3109,11 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" s="15">
       <c r="A26" s="14" t="n">
-        <v>100080004</v>
+        <v>100080005</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-4</t>
+          <t>洞府土地庙1-5</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -3118,26 +3128,26 @@
         <v>10005</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>10070</v>
+        <v>10044</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="J26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>3002</v>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7" t="n">
         <v>3003</v>
       </c>
-      <c r="K26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="7" t="n">
+      <c r="N26" s="7" t="n">
         <v>3004</v>
       </c>
-      <c r="N26" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" s="9" t="n">
         <v>0</v>
       </c>
@@ -3147,8 +3157,8 @@
       <c r="Q26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="R26" s="7" t="n">
-        <v>3003</v>
+      <c r="R26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S26" s="9" t="n">
         <v>0</v>
@@ -3159,11 +3169,11 @@
     </row>
     <row r="27" ht="16.5" customHeight="1" s="15">
       <c r="A27" s="14" t="n">
-        <v>100080005</v>
+        <v>100080006</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-5</t>
+          <t>洞府土地庙2-1</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -3178,22 +3188,22 @@
         <v>10005</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>10044</v>
+        <v>10066</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="L27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="7" t="n">
+      <c r="J27" s="7" t="n">
+        <v>3004</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="7" t="n">
         <v>3003</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="N27" s="7" t="n">
         <v>3004</v>
@@ -3219,11 +3229,11 @@
     </row>
     <row r="28" ht="16.5" customHeight="1" s="15">
       <c r="A28" s="14" t="n">
-        <v>100080006</v>
+        <v>100080007</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-1</t>
+          <t>洞府土地庙2-2</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -3238,19 +3248,19 @@
         <v>10005</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>10066</v>
+        <v>10070</v>
       </c>
       <c r="I28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="M28" s="9" t="n">
         <v>0</v>
@@ -3261,8 +3271,8 @@
       <c r="O28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P28" s="9" t="n">
-        <v>0</v>
+      <c r="P28" s="7" t="n">
+        <v>3003</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -3279,11 +3289,11 @@
     </row>
     <row r="29" ht="16.5" customHeight="1" s="15">
       <c r="A29" s="14" t="n">
-        <v>100080007</v>
+        <v>100080008</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-2</t>
+          <t>洞府土地庙2-3</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -3298,10 +3308,10 @@
         <v>10005</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>10070</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>0</v>
+        <v>10066</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>3004</v>
       </c>
       <c r="J29" s="7" t="n">
         <v>3002</v>
@@ -3310,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="M29" s="9" t="n">
         <v>0</v>
@@ -3321,8 +3331,8 @@
       <c r="O29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P29" s="7" t="n">
-        <v>3003</v>
+      <c r="P29" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3339,11 +3349,11 @@
     </row>
     <row r="30" ht="16.5" customHeight="1" s="15">
       <c r="A30" s="14" t="n">
-        <v>100080008</v>
+        <v>100080009</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-3</t>
+          <t>洞府土地庙2-4</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3358,37 +3368,37 @@
         <v>10005</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>10066</v>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>3004</v>
+        <v>10070</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J30" s="7" t="n">
+        <v>3003</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="7" t="n">
+        <v>3003</v>
+      </c>
+      <c r="Q30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="7" t="n">
         <v>3002</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="7" t="n">
-        <v>3003</v>
-      </c>
-      <c r="M30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="7" t="n">
-        <v>3004</v>
-      </c>
-      <c r="O30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="S30" s="9" t="n">
         <v>0</v>
@@ -3399,11 +3409,11 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" s="15">
       <c r="A31" s="14" t="n">
-        <v>100080009</v>
+        <v>100080010</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-4</t>
+          <t>洞府土地庙2-5</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -3418,37 +3428,37 @@
         <v>10005</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>10070</v>
+        <v>10066</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="7" t="n">
+        <v>3002</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>3004</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="7" t="n">
         <v>3003</v>
       </c>
-      <c r="K31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="P31" s="7" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="R31" s="7" t="n">
-        <v>3002</v>
+      <c r="R31" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S31" s="9" t="n">
         <v>0</v>
@@ -3459,16 +3469,16 @@
     </row>
     <row r="32" ht="16.5" customHeight="1" s="15">
       <c r="A32" s="14" t="n">
-        <v>100080010</v>
+        <v>100140001</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-5</t>
+          <t>攻城战pvp战斗</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>TEMPLE</t>
+          <t>SIEGE</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
@@ -3477,41 +3487,38 @@
       <c r="E32" s="8" t="n">
         <v>10005</v>
       </c>
-      <c r="F32" s="13" t="n">
-        <v>10066</v>
-      </c>
       <c r="I32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="7" t="n">
-        <v>3002</v>
+        <v>5024</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>5024</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="7" t="n">
-        <v>3004</v>
+        <v>5024</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>5024</v>
       </c>
       <c r="M32" s="9" t="n">
-        <v>0</v>
+        <v>5024</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="7" t="n">
-        <v>3003</v>
-      </c>
-      <c r="P32" s="7" t="n">
-        <v>3002</v>
+        <v>5024</v>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>5024</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>0</v>
+        <v>5024</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>0</v>
+        <v>5024</v>
       </c>
       <c r="S32" s="9" t="n">
-        <v>0</v>
+        <v>5024</v>
       </c>
       <c r="T32" s="9" t="n">
         <v>0</v>
@@ -3519,14 +3526,14 @@
     </row>
     <row r="33" ht="16.5" customHeight="1" s="15">
       <c r="A33" s="14" t="n">
-        <v>100140001</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>攻城战pvp战斗</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
+        <v>100140002</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>攻城战守军战斗1</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>SIEGE</t>
         </is>
@@ -3537,50 +3544,31 @@
       <c r="E33" s="8" t="n">
         <v>10005</v>
       </c>
-      <c r="I33" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="L33" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="M33" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="N33" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="O33" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="P33" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I33" s="7" t="n">
+        <v>10014</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>10014</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>10014</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>10014</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>10014</v>
+      </c>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n">
-        <v>100140002</v>
+        <v>100140003</v>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>攻城战守军战斗1</t>
+          <t>攻城战守军战斗2</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -3595,30 +3583,30 @@
         <v>10005</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>10014</v>
+        <v>10017</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>10014</v>
+        <v>10017</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>10014</v>
+        <v>10017</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>10014</v>
+        <v>10017</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>10014</v>
+        <v>10017</v>
       </c>
       <c r="N34" s="7" t="n"/>
       <c r="O34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n">
-        <v>100140003</v>
+        <v>100140004</v>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>攻城战守军战斗2</t>
+          <t>攻城战守军战斗3</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -3636,152 +3624,43 @@
       <c r="G35" s="22" t="n"/>
       <c r="H35" s="22" t="n"/>
       <c r="I35" s="7" t="n">
-        <v>10017</v>
+        <v>10020</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>10017</v>
+        <v>10020</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>10017</v>
+        <v>10020</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>10017</v>
+        <v>10020</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>10017</v>
+        <v>10020</v>
       </c>
       <c r="N35" s="7" t="n"/>
       <c r="O35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="n">
-        <v>100140004</v>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>攻城战守军战斗3</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>SIEGE</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>1</v>
-      </c>
+        <v>100140005</v>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n">
-        <v>10005</v>
+        <v>10070</v>
       </c>
       <c r="F36" s="22" t="n"/>
       <c r="G36" s="22" t="n"/>
       <c r="H36" s="22" t="n"/>
-      <c r="I36" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="J36" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="L36" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="M36" s="7" t="n">
-        <v>10020</v>
-      </c>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="7" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="14" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="n">
-        <v>100140005</v>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>魔龙 Razak</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>PVE</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n">
-        <v>10051</v>
-      </c>
-      <c r="F37" s="22" t="n">
-        <v>100600</v>
-      </c>
-      <c r="G37" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>25060001</v>
-      </c>
-      <c r="J37" s="7" t="n">
-        <v>25060001</v>
-      </c>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
-      <c r="N37" s="7" t="n"/>
-      <c r="O37" s="14" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="n">
-        <v>100140006</v>
-      </c>
-      <c r="B38" s="14" t="n"/>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>BOSS</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n">
-        <v>10052</v>
-      </c>
-      <c r="F38" s="22" t="n"/>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="22" t="n"/>
-      <c r="I38" s="7" t="n"/>
-      <c r="J38" s="7" t="n"/>
-      <c r="K38" s="7" t="n"/>
-      <c r="L38" s="7" t="n"/>
-      <c r="M38" s="7" t="n"/>
-      <c r="N38" s="7" t="n"/>
-      <c r="O38" s="14" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="n">
-        <v>100140007</v>
-      </c>
-      <c r="B39" s="14" t="n"/>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>BOSS</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n">
-        <v>10053</v>
-      </c>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="22" t="n"/>
-      <c r="H39" s="22" t="n"/>
-      <c r="I39" s="7" t="n"/>
-      <c r="J39" s="7" t="n"/>
-      <c r="K39" s="7" t="n"/>
-      <c r="L39" s="7" t="n"/>
-      <c r="M39" s="7" t="n"/>
-      <c r="N39" s="7" t="n"/>
-      <c r="O39" s="14" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A14">

--- a/resources/combat/combat.xlsx
+++ b/resources/combat/combat.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="752" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="combat_data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="combat_data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">combat_data!#REF!</definedName>
@@ -1780,7 +1780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.125" customWidth="1" style="3" min="1" max="1"/>
@@ -3662,6 +3662,31 @@
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="14" t="n"/>
     </row>
+    <row r="37">
+      <c r="A37" s="14" t="n">
+        <v>100140006</v>
+      </c>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>副本战斗</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n">
+        <v>10070</v>
+      </c>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="22" t="n"/>
+      <c r="H37" s="22" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="7" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="14" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A14">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>

--- a/resources/combat/combat.xlsx
+++ b/resources/combat/combat.xlsx
@@ -1780,7 +1780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.125" customWidth="1" style="3" min="1" max="1"/>
@@ -2621,247 +2621,173 @@
       <c r="T16" s="9" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="15">
-      <c r="A17" s="7" t="n">
-        <v>100011000</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>低级灵脉战</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>10005</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>10033</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="A17" s="14" t="n">
+        <v>25082001</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>长老试炼</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="22" t="n">
+        <v>100821</v>
+      </c>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="7" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="9" t="n"/>
+      <c r="T17" s="9" t="n"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="15">
-      <c r="A18" s="7" t="n">
-        <v>100011001</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>中级灵脉战</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n"/>
+      <c r="A18" s="14" t="n">
+        <v>25083001</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>第一环250830击退前锋</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>击退前锋</t>
+        </is>
+      </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>10005</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>10034</v>
+        <v>250830</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>100830</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>3000</v>
+        <v>250831</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>3001</v>
-      </c>
-      <c r="L18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="15">
-      <c r="A19" s="7" t="n">
-        <v>100011002</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>高级灵脉战</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n"/>
+      <c r="A19" s="14" t="n">
+        <v>25083002</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>第二环250831捣毁巢穴目标</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>捣毁巢穴</t>
+        </is>
+      </c>
       <c r="D19" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>10005</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>10035</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>3001</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>3001</v>
-      </c>
-      <c r="M19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>250831</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>100831</v>
+      </c>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="7" t="n"/>
+      <c r="O19" s="14" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="22" t="n"/>
+      <c r="S19" s="22" t="n"/>
+      <c r="T19" s="22" t="n"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="15">
       <c r="A20" s="14" t="n">
-        <v>100080001</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>洞府土地庙1-1</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>TEMPLE</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>10005</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>10044</v>
+        <v>25083003</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>第三环250832讨伐兽王目标</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>讨伐兽王</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="22" t="n">
+        <v>100832</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="7" t="n">
-        <v>3003</v>
-      </c>
-      <c r="M20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>250832</v>
+      </c>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="7" t="n"/>
+      <c r="O20" s="14" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="n"/>
+      <c r="S20" s="22" t="n"/>
+      <c r="T20" s="22" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="15">
-      <c r="A21" s="14" t="n">
-        <v>100080002</v>
+      <c r="A21" s="7" t="n">
+        <v>100011000</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-2</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>TEMPLE</t>
-        </is>
-      </c>
+          <t>低级灵脉战</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n">
         <v>1</v>
       </c>
@@ -2869,16 +2795,16 @@
         <v>10005</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>10068</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>3002</v>
+        <v>10033</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>0</v>
@@ -2886,8 +2812,8 @@
       <c r="M21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="7" t="n">
-        <v>3004</v>
+      <c r="N21" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="O21" s="9" t="n">
         <v>0</v>
@@ -2909,19 +2835,15 @@
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="15">
-      <c r="A22" s="14" t="n">
-        <v>100080003</v>
+      <c r="A22" s="7" t="n">
+        <v>100011001</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-3</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>TEMPLE</t>
-        </is>
-      </c>
+          <t>中级灵脉战</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n">
         <v>1</v>
       </c>
@@ -2929,25 +2851,25 @@
         <v>10005</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>10050</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="7" t="n">
-        <v>3003</v>
+        <v>10034</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>3001</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="7" t="n">
-        <v>3002</v>
+      <c r="N22" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="O22" s="9" t="n">
         <v>0</v>
@@ -2969,19 +2891,15 @@
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="15">
-      <c r="A23" s="14" t="n">
-        <v>100080004</v>
+      <c r="A23" s="7" t="n">
+        <v>100011002</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-4</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>TEMPLE</t>
-        </is>
-      </c>
+          <t>高级灵脉战</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n">
         <v>1</v>
       </c>
@@ -2989,22 +2907,22 @@
         <v>10005</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>10070</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>0</v>
+        <v>10035</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>3000</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>3003</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="7" t="n">
-        <v>3004</v>
+        <v>3000</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>3001</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>3001</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="N23" s="9" t="n">
         <v>0</v>
@@ -3018,8 +2936,8 @@
       <c r="Q23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="R23" s="7" t="n">
-        <v>3003</v>
+      <c r="R23" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S23" s="9" t="n">
         <v>0</v>
@@ -3030,11 +2948,11 @@
     </row>
     <row r="24" ht="16.5" customHeight="1" s="15">
       <c r="A24" s="14" t="n">
-        <v>100080005</v>
+        <v>100080001</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-5</t>
+          <t>洞府土地庙1-1</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -3051,23 +2969,23 @@
       <c r="F24" s="13" t="n">
         <v>10044</v>
       </c>
-      <c r="I24" s="9" t="n">
-        <v>0</v>
+      <c r="I24" s="7" t="n">
+        <v>3002</v>
       </c>
       <c r="J24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="7" t="n">
+      <c r="K24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7" t="n">
         <v>3003</v>
       </c>
-      <c r="N24" s="7" t="n">
-        <v>3004</v>
+      <c r="M24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="O24" s="9" t="n">
         <v>0</v>
@@ -3090,11 +3008,11 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" s="15">
       <c r="A25" s="14" t="n">
-        <v>100080006</v>
+        <v>100080002</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-1</t>
+          <t>洞府土地庙1-2</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3109,19 +3027,19 @@
         <v>10005</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>10066</v>
+        <v>10068</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="7" t="n">
-        <v>3004</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="7" t="n">
-        <v>3003</v>
+      <c r="J25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>3002</v>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="9" t="n">
         <v>0</v>
@@ -3150,11 +3068,11 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" s="15">
       <c r="A26" s="14" t="n">
-        <v>100080007</v>
+        <v>100080003</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-2</t>
+          <t>洞府土地庙1-3</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -3169,31 +3087,31 @@
         <v>10005</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>10070</v>
+        <v>10050</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="J26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>3003</v>
+      </c>
+      <c r="M26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="7" t="n">
         <v>3002</v>
       </c>
-      <c r="K26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="M26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>3004</v>
-      </c>
       <c r="O26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P26" s="7" t="n">
-        <v>3003</v>
+      <c r="P26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>0</v>
@@ -3210,11 +3128,11 @@
     </row>
     <row r="27" ht="16.5" customHeight="1" s="15">
       <c r="A27" s="14" t="n">
-        <v>100080008</v>
+        <v>100080004</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-3</t>
+          <t>洞府土地庙1-4</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -3229,37 +3147,37 @@
         <v>10005</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>10066</v>
-      </c>
-      <c r="I27" s="7" t="n">
+        <v>10070</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>3003</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="7" t="n">
         <v>3004</v>
       </c>
-      <c r="J27" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="7" t="n">
+      <c r="N27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="7" t="n">
         <v>3003</v>
-      </c>
-      <c r="M27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="7" t="n">
-        <v>3004</v>
-      </c>
-      <c r="O27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="S27" s="9" t="n">
         <v>0</v>
@@ -3270,11 +3188,11 @@
     </row>
     <row r="28" ht="16.5" customHeight="1" s="15">
       <c r="A28" s="14" t="n">
-        <v>100080009</v>
+        <v>100080005</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-4</t>
+          <t>洞府土地庙1-5</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -3289,37 +3207,37 @@
         <v>10005</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>10070</v>
+        <v>10044</v>
       </c>
       <c r="I28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="J28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>3002</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="7" t="n">
         <v>3003</v>
       </c>
-      <c r="K28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="9" t="n">
-        <v>0</v>
+      <c r="N28" s="7" t="n">
+        <v>3004</v>
       </c>
       <c r="O28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P28" s="7" t="n">
-        <v>3003</v>
+      <c r="P28" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="R28" s="7" t="n">
-        <v>3002</v>
+      <c r="R28" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S28" s="9" t="n">
         <v>0</v>
@@ -3330,11 +3248,11 @@
     </row>
     <row r="29" ht="16.5" customHeight="1" s="15">
       <c r="A29" s="14" t="n">
-        <v>100080010</v>
+        <v>100080006</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-5</t>
+          <t>洞府土地庙2-1</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -3355,25 +3273,25 @@
         <v>0</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>3002</v>
+        <v>3004</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="7" t="n">
+        <v>3003</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="7" t="n">
         <v>3004</v>
       </c>
-      <c r="M29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="7" t="n">
-        <v>3003</v>
-      </c>
-      <c r="P29" s="7" t="n">
-        <v>3002</v>
+      <c r="O29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3390,16 +3308,16 @@
     </row>
     <row r="30" ht="16.5" customHeight="1" s="15">
       <c r="A30" s="14" t="n">
-        <v>100140001</v>
+        <v>100080007</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>攻城战pvp战斗</t>
+          <t>洞府土地庙2-2</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>SIEGE</t>
+          <t>TEMPLE</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
@@ -3408,38 +3326,41 @@
       <c r="E30" s="8" t="n">
         <v>10005</v>
       </c>
+      <c r="F30" s="13" t="n">
+        <v>10070</v>
+      </c>
       <c r="I30" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>5024</v>
+        <v>0</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>3002</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="L30" s="9" t="n">
-        <v>5024</v>
+        <v>0</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>3002</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="N30" s="9" t="n">
-        <v>5024</v>
+        <v>0</v>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>3004</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="P30" s="9" t="n">
-        <v>5024</v>
+        <v>0</v>
+      </c>
+      <c r="P30" s="7" t="n">
+        <v>3003</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>5024</v>
+        <v>0</v>
       </c>
       <c r="R30" s="9" t="n">
-        <v>5024</v>
+        <v>0</v>
       </c>
       <c r="S30" s="9" t="n">
-        <v>5024</v>
+        <v>0</v>
       </c>
       <c r="T30" s="9" t="n">
         <v>0</v>
@@ -3447,16 +3368,16 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" s="15">
       <c r="A31" s="14" t="n">
-        <v>100140002</v>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>攻城战守军战斗1</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>SIEGE</t>
+        <v>100080008</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>洞府土地庙2-3</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>TEMPLE</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
@@ -3465,36 +3386,58 @@
       <c r="E31" s="8" t="n">
         <v>10005</v>
       </c>
+      <c r="F31" s="13" t="n">
+        <v>10066</v>
+      </c>
       <c r="I31" s="7" t="n">
-        <v>10014</v>
+        <v>3004</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>10014</v>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>10014</v>
+        <v>3002</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>10014</v>
-      </c>
-      <c r="M31" s="7" t="n">
-        <v>10014</v>
-      </c>
-      <c r="N31" s="7" t="n"/>
-      <c r="O31" s="14" t="n"/>
+        <v>3003</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>3004</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="15">
       <c r="A32" s="14" t="n">
-        <v>100140003</v>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>攻城战守军战斗2</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>SIEGE</t>
+        <v>100080009</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>洞府土地庙2-4</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>TEMPLE</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
@@ -3503,36 +3446,58 @@
       <c r="E32" s="8" t="n">
         <v>10005</v>
       </c>
-      <c r="I32" s="7" t="n">
-        <v>10017</v>
+      <c r="F32" s="13" t="n">
+        <v>10070</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>10017</v>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>10017</v>
-      </c>
-      <c r="L32" s="7" t="n">
-        <v>10017</v>
-      </c>
-      <c r="M32" s="7" t="n">
-        <v>10017</v>
-      </c>
-      <c r="N32" s="7" t="n"/>
-      <c r="O32" s="14" t="n"/>
+        <v>3003</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="7" t="n">
+        <v>3003</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>3002</v>
+      </c>
+      <c r="S32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="15">
       <c r="A33" s="14" t="n">
-        <v>100140004</v>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>攻城战守军战斗3</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>SIEGE</t>
+        <v>100080010</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>洞府土地庙2-5</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>TEMPLE</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
@@ -3541,112 +3506,324 @@
       <c r="E33" s="8" t="n">
         <v>10005</v>
       </c>
-      <c r="I33" s="7" t="n">
-        <v>10020</v>
+      <c r="F33" s="13" t="n">
+        <v>10066</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>10020</v>
+        <v>3002</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="M33" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="N33" s="7" t="n"/>
-      <c r="O33" s="14" t="n"/>
+        <v>3004</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="7" t="n">
+        <v>3003</v>
+      </c>
+      <c r="P33" s="7" t="n">
+        <v>3002</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n">
-        <v>100140005</v>
-      </c>
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="8" t="n"/>
+        <v>100140001</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>攻城战pvp战斗</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>SIEGE</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="E34" s="8" t="n">
-        <v>10050</v>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>25083001</v>
-      </c>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n"/>
-      <c r="O34" s="14" t="n"/>
+        <v>10005</v>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="M34" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="P34" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="R34" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="S34" s="9" t="n">
+        <v>5024</v>
+      </c>
+      <c r="T34" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n">
-        <v>100140006</v>
+        <v>100140002</v>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>兽王·第一场</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="22" t="n">
-        <v>100830</v>
-      </c>
-      <c r="I35" s="7" t="n"/>
-      <c r="J35" s="7" t="n"/>
-      <c r="K35" s="7" t="n"/>
-      <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
+          <t>攻城战守军战斗1</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>SIEGE</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F35" s="22" t="n"/>
+      <c r="I35" s="7" t="n">
+        <v>10014</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>10014</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>10014</v>
+      </c>
+      <c r="L35" s="7" t="n">
+        <v>10014</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>10014</v>
+      </c>
       <c r="N35" s="7" t="n"/>
       <c r="O35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="n">
-        <v>100140007</v>
+        <v>100140003</v>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>兽王·第二场</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="22" t="n">
-        <v>100831</v>
-      </c>
-      <c r="I36" s="7" t="n"/>
-      <c r="J36" s="7" t="n"/>
-      <c r="K36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
+          <t>攻城战守军战斗2</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>SIEGE</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F36" s="22" t="n"/>
+      <c r="I36" s="7" t="n">
+        <v>10017</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>10017</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>10017</v>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>10017</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>10017</v>
+      </c>
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n">
-        <v>100140008</v>
+        <v>100140004</v>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>兽王·第三场</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="22" t="n">
-        <v>100832</v>
-      </c>
-      <c r="I37" s="7" t="n"/>
-      <c r="J37" s="7" t="n"/>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
+          <t>攻城战守军战斗3</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>SIEGE</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F37" s="22" t="n"/>
+      <c r="I37" s="7" t="n">
+        <v>10020</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>10020</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>10020</v>
+      </c>
+      <c r="L37" s="7" t="n">
+        <v>10020</v>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>10020</v>
+      </c>
       <c r="N37" s="7" t="n"/>
       <c r="O37" s="14" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="n">
+        <v>100140005</v>
+      </c>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n">
+        <v>10050</v>
+      </c>
+      <c r="F38" s="22" t="n"/>
+      <c r="I38" s="7" t="n">
+        <v>25083001</v>
+      </c>
+      <c r="J38" s="7" t="n"/>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
+      <c r="N38" s="7" t="n"/>
+      <c r="O38" s="14" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="n">
+        <v>100140006</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>兽王·第一场</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="22" t="n">
+        <v>100830</v>
+      </c>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="7" t="n"/>
+      <c r="K39" s="7" t="n"/>
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
+      <c r="N39" s="7" t="n"/>
+      <c r="O39" s="14" t="n"/>
+      <c r="P39" s="0" t="n"/>
+      <c r="Q39" s="0" t="n"/>
+      <c r="R39" s="0" t="n"/>
+      <c r="S39" s="0" t="n"/>
+      <c r="T39" s="0" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="n">
+        <v>100140007</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>兽王·第二场</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="22" t="n">
+        <v>100831</v>
+      </c>
+      <c r="I40" s="7" t="n"/>
+      <c r="J40" s="7" t="n"/>
+      <c r="K40" s="7" t="n"/>
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
+      <c r="N40" s="7" t="n"/>
+      <c r="O40" s="14" t="n"/>
+      <c r="P40" s="22" t="n"/>
+      <c r="Q40" s="22" t="n"/>
+      <c r="R40" s="22" t="n"/>
+      <c r="S40" s="22" t="n"/>
+      <c r="T40" s="22" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="n">
+        <v>100140008</v>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>兽王·第三场</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="22" t="n">
+        <v>100832</v>
+      </c>
+      <c r="I41" s="7" t="n"/>
+      <c r="J41" s="7" t="n"/>
+      <c r="K41" s="7" t="n"/>
+      <c r="L41" s="7" t="n"/>
+      <c r="M41" s="7" t="n"/>
+      <c r="N41" s="7" t="n"/>
+      <c r="O41" s="14" t="n"/>
+      <c r="P41" s="22" t="n"/>
+      <c r="Q41" s="22" t="n"/>
+      <c r="R41" s="22" t="n"/>
+      <c r="S41" s="22" t="n"/>
+      <c r="T41" s="22" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A14">

--- a/resources/combat/combat.xlsx
+++ b/resources/combat/combat.xlsx
@@ -1780,7 +1780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.125" customWidth="1" style="3" min="1" max="1"/>
@@ -2621,173 +2621,247 @@
       <c r="T16" s="9" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="15">
-      <c r="A17" s="14" t="n">
-        <v>25082001</v>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>长老试炼</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="22" t="n">
-        <v>100821</v>
-      </c>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="9" t="n"/>
-      <c r="R17" s="9" t="n"/>
-      <c r="S17" s="9" t="n"/>
-      <c r="T17" s="9" t="n"/>
+      <c r="A17" s="7" t="n">
+        <v>100011000</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>低级灵脉战</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>10033</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="15">
-      <c r="A18" s="14" t="n">
-        <v>25083001</v>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>第一环250830击退前锋</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>击退前锋</t>
-        </is>
-      </c>
+      <c r="A18" s="7" t="n">
+        <v>100011001</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>中级灵脉战</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>250830</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>100830</v>
+        <v>10005</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>10034</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>250831</v>
+        <v>3000</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="22" t="n">
+        <v>3001</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="15">
-      <c r="A19" s="14" t="n">
-        <v>25083002</v>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>第二环250831捣毁巢穴目标</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>捣毁巢穴</t>
-        </is>
-      </c>
+      <c r="A19" s="7" t="n">
+        <v>100011002</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>高级灵脉战</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>250831</v>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>100831</v>
-      </c>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="22" t="n"/>
-      <c r="R19" s="22" t="n"/>
-      <c r="S19" s="22" t="n"/>
-      <c r="T19" s="22" t="n"/>
+        <v>10005</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>10035</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>3001</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>3001</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="15">
       <c r="A20" s="14" t="n">
-        <v>25083003</v>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>第三环250832讨伐兽王目标</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>讨伐兽王</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="22" t="n">
-        <v>100832</v>
+        <v>100080001</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>洞府土地庙1-1</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>TEMPLE</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>10044</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>250832</v>
-      </c>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n"/>
-      <c r="O20" s="14" t="n"/>
-      <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="22" t="n"/>
-      <c r="R20" s="22" t="n"/>
-      <c r="S20" s="22" t="n"/>
-      <c r="T20" s="22" t="n"/>
+        <v>3002</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>3003</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="15">
-      <c r="A21" s="7" t="n">
-        <v>100011000</v>
+      <c r="A21" s="14" t="n">
+        <v>100080002</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>低级灵脉战</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n"/>
+          <t>洞府土地庙1-2</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>TEMPLE</t>
+        </is>
+      </c>
       <c r="D21" s="8" t="n">
         <v>1</v>
       </c>
@@ -2795,16 +2869,16 @@
         <v>10005</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>10033</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>0</v>
+        <v>10068</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>3002</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>0</v>
@@ -2812,8 +2886,8 @@
       <c r="M21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="9" t="n">
-        <v>0</v>
+      <c r="N21" s="7" t="n">
+        <v>3004</v>
       </c>
       <c r="O21" s="9" t="n">
         <v>0</v>
@@ -2835,15 +2909,19 @@
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="15">
-      <c r="A22" s="7" t="n">
-        <v>100011001</v>
+      <c r="A22" s="14" t="n">
+        <v>100080003</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>中级灵脉战</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n"/>
+          <t>洞府土地庙1-3</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>TEMPLE</t>
+        </is>
+      </c>
       <c r="D22" s="8" t="n">
         <v>1</v>
       </c>
@@ -2851,25 +2929,25 @@
         <v>10005</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>10034</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>3001</v>
-      </c>
-      <c r="L22" s="9" t="n">
-        <v>0</v>
+        <v>10050</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>3003</v>
       </c>
       <c r="M22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="9" t="n">
-        <v>0</v>
+      <c r="N22" s="7" t="n">
+        <v>3002</v>
       </c>
       <c r="O22" s="9" t="n">
         <v>0</v>
@@ -2891,15 +2969,19 @@
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="15">
-      <c r="A23" s="7" t="n">
-        <v>100011002</v>
+      <c r="A23" s="14" t="n">
+        <v>100080004</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>高级灵脉战</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
+          <t>洞府土地庙1-4</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>TEMPLE</t>
+        </is>
+      </c>
       <c r="D23" s="8" t="n">
         <v>1</v>
       </c>
@@ -2907,22 +2989,22 @@
         <v>10005</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>10035</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>3000</v>
+        <v>10070</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>3001</v>
-      </c>
-      <c r="L23" s="7" t="n">
-        <v>3001</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>0</v>
+        <v>3003</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>3004</v>
       </c>
       <c r="N23" s="9" t="n">
         <v>0</v>
@@ -2936,8 +3018,8 @@
       <c r="Q23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="R23" s="9" t="n">
-        <v>0</v>
+      <c r="R23" s="7" t="n">
+        <v>3003</v>
       </c>
       <c r="S23" s="9" t="n">
         <v>0</v>
@@ -2948,11 +3030,11 @@
     </row>
     <row r="24" ht="16.5" customHeight="1" s="15">
       <c r="A24" s="14" t="n">
-        <v>100080001</v>
+        <v>100080005</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-1</t>
+          <t>洞府土地庙1-5</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -2969,23 +3051,23 @@
       <c r="F24" s="13" t="n">
         <v>10044</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="7" t="n">
         <v>3002</v>
       </c>
-      <c r="J24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="7" t="n">
+      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="7" t="n">
         <v>3003</v>
       </c>
-      <c r="M24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="9" t="n">
-        <v>0</v>
+      <c r="N24" s="7" t="n">
+        <v>3004</v>
       </c>
       <c r="O24" s="9" t="n">
         <v>0</v>
@@ -3008,11 +3090,11 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" s="15">
       <c r="A25" s="14" t="n">
-        <v>100080002</v>
+        <v>100080006</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-2</t>
+          <t>洞府土地庙2-1</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3027,19 +3109,19 @@
         <v>10005</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>10068</v>
+        <v>10066</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="L25" s="9" t="n">
-        <v>0</v>
+      <c r="J25" s="7" t="n">
+        <v>3004</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>3003</v>
       </c>
       <c r="M25" s="9" t="n">
         <v>0</v>
@@ -3068,11 +3150,11 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" s="15">
       <c r="A26" s="14" t="n">
-        <v>100080003</v>
+        <v>100080007</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-3</t>
+          <t>洞府土地庙2-2</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -3087,31 +3169,31 @@
         <v>10005</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>10050</v>
+        <v>10070</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="9" t="n">
-        <v>0</v>
+      <c r="J26" s="7" t="n">
+        <v>3002</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="7" t="n">
+        <v>3002</v>
+      </c>
+      <c r="M26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>3004</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="7" t="n">
         <v>3003</v>
-      </c>
-      <c r="M26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="O26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>0</v>
@@ -3128,11 +3210,11 @@
     </row>
     <row r="27" ht="16.5" customHeight="1" s="15">
       <c r="A27" s="14" t="n">
-        <v>100080004</v>
+        <v>100080008</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-4</t>
+          <t>洞府土地庙2-3</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -3147,26 +3229,26 @@
         <v>10005</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>10070</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>0</v>
+        <v>10066</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>3004</v>
       </c>
       <c r="J27" s="7" t="n">
+        <v>3002</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="7" t="n">
         <v>3003</v>
       </c>
-      <c r="K27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="7" t="n">
         <v>3004</v>
       </c>
-      <c r="N27" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="O27" s="9" t="n">
         <v>0</v>
       </c>
@@ -3176,8 +3258,8 @@
       <c r="Q27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="R27" s="7" t="n">
-        <v>3003</v>
+      <c r="R27" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S27" s="9" t="n">
         <v>0</v>
@@ -3188,11 +3270,11 @@
     </row>
     <row r="28" ht="16.5" customHeight="1" s="15">
       <c r="A28" s="14" t="n">
-        <v>100080005</v>
+        <v>100080009</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙1-5</t>
+          <t>洞府土地庙2-4</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -3207,37 +3289,37 @@
         <v>10005</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>10044</v>
+        <v>10070</v>
       </c>
       <c r="I28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="7" t="n">
+      <c r="J28" s="7" t="n">
+        <v>3003</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="7" t="n">
+        <v>3003</v>
+      </c>
+      <c r="Q28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="7" t="n">
         <v>3002</v>
-      </c>
-      <c r="L28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="7" t="n">
-        <v>3003</v>
-      </c>
-      <c r="N28" s="7" t="n">
-        <v>3004</v>
-      </c>
-      <c r="O28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="S28" s="9" t="n">
         <v>0</v>
@@ -3248,11 +3330,11 @@
     </row>
     <row r="29" ht="16.5" customHeight="1" s="15">
       <c r="A29" s="14" t="n">
-        <v>100080006</v>
+        <v>100080010</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-1</t>
+          <t>洞府土地庙2-5</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -3273,25 +3355,25 @@
         <v>0</v>
       </c>
       <c r="J29" s="7" t="n">
+        <v>3002</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="7" t="n">
         <v>3004</v>
       </c>
-      <c r="K29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="7" t="n">
+      <c r="M29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="7" t="n">
         <v>3003</v>
       </c>
-      <c r="M29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="7" t="n">
-        <v>3004</v>
-      </c>
-      <c r="O29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="9" t="n">
-        <v>0</v>
+      <c r="P29" s="7" t="n">
+        <v>3002</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3308,16 +3390,16 @@
     </row>
     <row r="30" ht="16.5" customHeight="1" s="15">
       <c r="A30" s="14" t="n">
-        <v>100080007</v>
+        <v>100140001</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>洞府土地庙2-2</t>
+          <t>攻城战pvp战斗</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>TEMPLE</t>
+          <t>SIEGE</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
@@ -3326,41 +3408,38 @@
       <c r="E30" s="8" t="n">
         <v>10005</v>
       </c>
-      <c r="F30" s="13" t="n">
-        <v>10070</v>
-      </c>
       <c r="I30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="7" t="n">
-        <v>3002</v>
+        <v>5024</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>5024</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="7" t="n">
-        <v>3002</v>
+        <v>5024</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>5024</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="7" t="n">
-        <v>3004</v>
+        <v>5024</v>
+      </c>
+      <c r="N30" s="9" t="n">
+        <v>5024</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="7" t="n">
-        <v>3003</v>
+        <v>5024</v>
+      </c>
+      <c r="P30" s="9" t="n">
+        <v>5024</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>0</v>
+        <v>5024</v>
       </c>
       <c r="R30" s="9" t="n">
-        <v>0</v>
+        <v>5024</v>
       </c>
       <c r="S30" s="9" t="n">
-        <v>0</v>
+        <v>5024</v>
       </c>
       <c r="T30" s="9" t="n">
         <v>0</v>
@@ -3368,16 +3447,16 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" s="15">
       <c r="A31" s="14" t="n">
-        <v>100080008</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>洞府土地庙2-3</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>TEMPLE</t>
+        <v>100140002</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>攻城战守军战斗1</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>SIEGE</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
@@ -3386,58 +3465,36 @@
       <c r="E31" s="8" t="n">
         <v>10005</v>
       </c>
-      <c r="F31" s="13" t="n">
-        <v>10066</v>
-      </c>
       <c r="I31" s="7" t="n">
-        <v>3004</v>
+        <v>10014</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="K31" s="9" t="n">
-        <v>0</v>
+        <v>10014</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>10014</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>3003</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="7" t="n">
-        <v>3004</v>
-      </c>
-      <c r="O31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>10014</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>10014</v>
+      </c>
+      <c r="N31" s="7" t="n"/>
+      <c r="O31" s="14" t="n"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="15">
       <c r="A32" s="14" t="n">
-        <v>100080009</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>洞府土地庙2-4</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>TEMPLE</t>
+        <v>100140003</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>攻城战守军战斗2</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>SIEGE</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
@@ -3446,58 +3503,36 @@
       <c r="E32" s="8" t="n">
         <v>10005</v>
       </c>
-      <c r="F32" s="13" t="n">
-        <v>10070</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>0</v>
+      <c r="I32" s="7" t="n">
+        <v>10017</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>3003</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="7" t="n">
-        <v>3003</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="S32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>10017</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>10017</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>10017</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>10017</v>
+      </c>
+      <c r="N32" s="7" t="n"/>
+      <c r="O32" s="14" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="15">
       <c r="A33" s="14" t="n">
-        <v>100080010</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>洞府土地庙2-5</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>TEMPLE</t>
+        <v>100140004</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>攻城战守军战斗3</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>SIEGE</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
@@ -3506,324 +3541,101 @@
       <c r="E33" s="8" t="n">
         <v>10005</v>
       </c>
-      <c r="F33" s="13" t="n">
-        <v>10066</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>0</v>
+      <c r="I33" s="7" t="n">
+        <v>10020</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>0</v>
+        <v>10020</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>10020</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>3004</v>
-      </c>
-      <c r="M33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="7" t="n">
-        <v>3003</v>
-      </c>
-      <c r="P33" s="7" t="n">
-        <v>3002</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>10020</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>10020</v>
+      </c>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n">
-        <v>100140001</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>攻城战pvp战斗</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>SIEGE</t>
+        <v>100140005</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>试炼小怪战</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>PVE</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>10005</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="L34" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="M34" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="N34" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="O34" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="P34" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="Q34" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="R34" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="S34" s="9" t="n">
-        <v>5024</v>
-      </c>
-      <c r="T34" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>10050</v>
+      </c>
+      <c r="F34" s="22" t="n">
+        <v>92001</v>
+      </c>
+      <c r="G34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>410001</v>
+      </c>
+      <c r="J34" s="7" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n">
-        <v>100140002</v>
+        <v>100140006</v>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>攻城战守军战斗1</t>
+          <t>试炼头目战</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>SIEGE</t>
+          <t>PVE</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>10005</v>
-      </c>
-      <c r="F35" s="22" t="n"/>
+        <v>10050</v>
+      </c>
+      <c r="F35" s="22" t="n">
+        <v>92002</v>
+      </c>
+      <c r="G35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="I35" s="7" t="n">
-        <v>10014</v>
-      </c>
-      <c r="J35" s="7" t="n">
-        <v>10014</v>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>10014</v>
-      </c>
-      <c r="L35" s="7" t="n">
-        <v>10014</v>
-      </c>
-      <c r="M35" s="7" t="n">
-        <v>10014</v>
-      </c>
+        <v>410002</v>
+      </c>
+      <c r="J35" s="7" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n"/>
       <c r="O35" s="14" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="n">
-        <v>100140003</v>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>攻城战守军战斗2</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>SIEGE</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>10005</v>
-      </c>
-      <c r="F36" s="22" t="n"/>
-      <c r="I36" s="7" t="n">
-        <v>10017</v>
-      </c>
-      <c r="J36" s="7" t="n">
-        <v>10017</v>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>10017</v>
-      </c>
-      <c r="L36" s="7" t="n">
-        <v>10017</v>
-      </c>
-      <c r="M36" s="7" t="n">
-        <v>10017</v>
-      </c>
-      <c r="N36" s="7" t="n"/>
-      <c r="O36" s="14" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="n">
-        <v>100140004</v>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>攻城战守军战斗3</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>SIEGE</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>10005</v>
-      </c>
-      <c r="F37" s="22" t="n"/>
-      <c r="I37" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="J37" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="L37" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="M37" s="7" t="n">
-        <v>10020</v>
-      </c>
-      <c r="N37" s="7" t="n"/>
-      <c r="O37" s="14" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="n">
-        <v>100140005</v>
-      </c>
-      <c r="B38" s="14" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n">
-        <v>10050</v>
-      </c>
-      <c r="F38" s="22" t="n"/>
-      <c r="I38" s="7" t="n">
-        <v>25083001</v>
-      </c>
-      <c r="J38" s="7" t="n"/>
-      <c r="K38" s="7" t="n"/>
-      <c r="L38" s="7" t="n"/>
-      <c r="M38" s="7" t="n"/>
-      <c r="N38" s="7" t="n"/>
-      <c r="O38" s="14" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="n">
-        <v>100140006</v>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>兽王·第一场</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="22" t="n">
-        <v>100830</v>
-      </c>
-      <c r="I39" s="7" t="n"/>
-      <c r="J39" s="7" t="n"/>
-      <c r="K39" s="7" t="n"/>
-      <c r="L39" s="7" t="n"/>
-      <c r="M39" s="7" t="n"/>
-      <c r="N39" s="7" t="n"/>
-      <c r="O39" s="14" t="n"/>
-      <c r="P39" s="0" t="n"/>
-      <c r="Q39" s="0" t="n"/>
-      <c r="R39" s="0" t="n"/>
-      <c r="S39" s="0" t="n"/>
-      <c r="T39" s="0" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="n">
-        <v>100140007</v>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>兽王·第二场</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="22" t="n">
-        <v>100831</v>
-      </c>
-      <c r="I40" s="7" t="n"/>
-      <c r="J40" s="7" t="n"/>
-      <c r="K40" s="7" t="n"/>
-      <c r="L40" s="7" t="n"/>
-      <c r="M40" s="7" t="n"/>
-      <c r="N40" s="7" t="n"/>
-      <c r="O40" s="14" t="n"/>
-      <c r="P40" s="22" t="n"/>
-      <c r="Q40" s="22" t="n"/>
-      <c r="R40" s="22" t="n"/>
-      <c r="S40" s="22" t="n"/>
-      <c r="T40" s="22" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="n">
-        <v>100140008</v>
-      </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>兽王·第三场</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n"/>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="22" t="n">
-        <v>100832</v>
-      </c>
-      <c r="I41" s="7" t="n"/>
-      <c r="J41" s="7" t="n"/>
-      <c r="K41" s="7" t="n"/>
-      <c r="L41" s="7" t="n"/>
-      <c r="M41" s="7" t="n"/>
-      <c r="N41" s="7" t="n"/>
-      <c r="O41" s="14" t="n"/>
-      <c r="P41" s="22" t="n"/>
-      <c r="Q41" s="22" t="n"/>
-      <c r="R41" s="22" t="n"/>
-      <c r="S41" s="22" t="n"/>
-      <c r="T41" s="22" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A14">
